--- a/assets/constructions/examples/ctd_mie_hf.xlsx
+++ b/assets/constructions/examples/ctd_mie_hf.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,41 +584,57 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EHF-ENMX06-D20Z3C20-L160</t>
+          <t>EXP-C32-33-200-3T</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ENMX 0604</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>20</v>
-      </c>
+          <t>EXP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>12.6</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>80</v>
-      </c>
-      <c r="I2" t="n">
-        <v>160</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>3</v>
       </c>
@@ -627,21 +643,25 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>1.19</v>
+      </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ENMX0604</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+          <t>WPMW06X415</t>
+        </is>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -654,91 +674,97 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>YG1_EN0604H</t>
+          <t>DER_WP06X4H</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>YG1_EN0604H</t>
+          <t>WP06X4_H</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
-        </is>
-      </c>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT115-032Z32R04FO09-L200</t>
+          <t>EHF-ENMX06-D16Z2C16-L150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MT115-Z...FO09-L..</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>ENMX 0604</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H3" t="n">
         <v>50</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>150</v>
+      </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FONT09T308..R</t>
+          <t>ENMX0604</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,16 +777,16 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>HA-32</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>SKIF_FO09T3H</t>
+          <t>YG1_EN0604H</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
         <v>4</v>
@@ -769,79 +795,91 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>SKIF_FO09T3H</t>
+          <t>YG1_EN0604H</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
+          <t>2021/YG1-TOOLING</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>209.53</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>19262.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VXF018Z02A18XP07L180</t>
+          <t>MT115-025W25R04FO06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VXF-07</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>18</v>
-      </c>
+          <t>MT115-W...FO06</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>8.952</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>180</v>
+        <v>118</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5.4</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>61000</v>
+        <v>15600</v>
       </c>
       <c r="N4" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="b">
+        <v>0.8</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>FONT06T205..R</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -850,12 +888,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>HA-18</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>WIDIA_XP0703H</t>
+          <t>SKIF_FO06T2H</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -868,81 +906,83 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>WID_XP0703_H</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>WID_VXF016_2801</t>
-        </is>
-      </c>
+          <t>SKIF_FO06T2H</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2019 / WIDIA достижения</t>
-        </is>
-      </c>
+          <t>2019/ Основной каталог СКИФ-М</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M370D032Z04A32WO08L200</t>
+          <t>MT115-032W32R03FO09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M370</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+          <t>MT115-W...FO09</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
         <v>32</v>
-      </c>
-      <c r="E5" t="n">
-        <v>18.06</v>
       </c>
       <c r="F5" t="n">
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>38700</v>
+        <v>16000</v>
       </c>
       <c r="N5" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FONT09T308..R</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -951,42 +991,44 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>HA-32</t>
+          <t>HB-32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>WIDIA_WO0804H</t>
+          <t>SKIF_FO09T3H</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>WID_WO0804_H</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>WID_M370D0_1241</t>
-        </is>
-      </c>
+          <t>SKIF_FO09T3H</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2017 / WIDIA основной каталог EN</t>
-        </is>
-      </c>
+          <t>2019/ Основной каталог СКИФ-М</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SKS-C32-33-200-2T</t>
+          <t>SKS-C32-33-160-2T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1007,7 +1049,7 @@
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="H6" t="n">
         <v>50</v>
@@ -1022,7 +1064,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>1.15</v>
+        <v>0.84</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1078,6 +1120,20 @@
         <is>
           <t>2019 / DEREK</t>
         </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>74.78</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>6130.01</v>
       </c>
     </row>
   </sheetData>
